--- a/output/template/接口模板-HTTP.xlsx
+++ b/output/template/接口模板-HTTP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/Fastapi-Vue/KeenRunner/backend/output/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/ForkRunner/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD79DA15-F1FC-D648-90E7-0053D8B1F311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3CCE90-5642-0544-BD5A-7F1F61067D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42340" yWindow="1640" windowWidth="36400" windowHeight="24260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,10 +89,6 @@
     <t>匹配规则</t>
   </si>
   <si>
-    <t>【必输字段】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>等于
 大于
 大于等于
@@ -136,62 +132,100 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>张三丰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>请求方式</t>
+  </si>
+  <si>
+    <t>请求路径</t>
+  </si>
+  <si>
+    <t>请求头</t>
+  </si>
+  <si>
+    <t>协议类型</t>
+  </si>
+  <si>
+    <t>请求体类型</t>
+  </si>
+  <si>
+    <t>【必输字段】
+相同应用下, 用例名称不允许重复</t>
+  </si>
+  <si>
+    <t>【必输字段】
+必须与项目管理中的配置名称完全一致</t>
+  </si>
+  <si>
+    <t>【必输字段】</t>
   </si>
   <si>
     <t>【建议填写字段】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>协议类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请求方式</t>
-  </si>
-  <si>
-    <t>请求路径</t>
-  </si>
-  <si>
-    <t>请求体类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请求头</t>
   </si>
   <si>
     <t>【必输字段】
 必须与环境管理中的配置名称完全一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【必输字段】
+选择项：json、xml、raw、form-data、x-www-form-urlencoded、none</t>
+  </si>
+  <si>
+    <t>【按需填写字段】
+[请求体类型]非none时必填</t>
+  </si>
+  <si>
+    <t>【按需填写字段】
+格式（描述非必填）
+key1:value1:描述1;
+key2:value2:描述2;</t>
+  </si>
+  <si>
+    <t>【按需填写字段】
+格式（描述非必填）
+（1）key1:value1:描述1;
+（2）key2:value2:描述2;</t>
+  </si>
+  <si>
+    <t>【按需填写字段】
+格式
+1、当提取来源不等于Request Text/Response Text：
+（1）变量名称1:提取来源:整个返回数据;
+（2）变量名称2:提取来源:提取部分:提取表达式2;
+2、当提取来源等于Request Text/Response Text：
+（1）变量名称1:提取来源:整个返回数据;
+（2）变量名称2:提取来源:提取部分:正则表达式2;
+（3）变量名称3:提取来源:提取部分:正则表达式3:匹配数字3;
+注：“整个返回数据”、“提取部分”均为提取范围"</t>
+  </si>
+  <si>
+    <t>【按需填写字段】
+格式
+1、当匹配规则不等于为空/不为空：
+（1）断言名称1:断言对象:断言表达式1:匹配规则:预期值1;
+（2）断言名称2:断言对象:断言表达式2:匹配规则:预期值2;
+2、当匹配规则等于为空/不为空：
+（1）断言名称1:断言对象:断言表达式1:匹配规则;
+（2）断言名称2:断言对象:断言表达式2:匹配规则;</t>
   </si>
   <si>
     <t>银联二维码消费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>快捷支付</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTTP</t>
   </si>
   <si>
     <t>union-serive/c2bConsume</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>POST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>银联联机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>/IFS.OP.union-service/c2bConsume</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>json</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{
@@ -218,90 +252,29 @@
     "SvcVerNo": "1.0"
   }
 }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>content-type:application/json
 SvcCd:SvcCd/json</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CrdNo:623185008900005215:卡号;
 CnsmrSrlNo:${generate_global_serial_number(channel_no=300103)}:消费方流水;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MsgTp:Request Json:整个返回数据;
 RSP_GlblSrlNo:Response Json:提取部分:$.Head.GlblSrlNo;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>RSP_TxnSt:Response Json:$.body.TxnSt:等于:S;
 global-variable:Response Json:$body.name:大于:M;
 identType:Response Json:$body.identTypeName:不为空;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【必输字段】
-相同应用下, 用例名称不允许重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【必输字段】
-必须与项目管理中的配置名称完全一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HTTP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【必输字段】
-选择项：json、xml、raw、form-data、x-www-form-urlencoded、none</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【按需填写字段】
-格式（描述非必填）
-key1:value1:描述1;
-key2:value2:描述2;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【按需填写字段】
-格式（描述非必填）
-（1）key1:value1:描述1;
-（2）key2:value2:描述2;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【按需填写字段】
-格式
-1、当提取来源不等于Request Text/Response Text：
-（1）变量名称1:提取来源:整个返回数据;
-（2）变量名称2:提取来源:提取部分:提取表达式2;
-2、当提取来源等于Request Text/Response Text：
-（1）变量名称1:提取来源:整个返回数据;
-（2）变量名称2:提取来源:提取部分:正则表达式2;
-（3）变量名称3:提取来源:提取部分:正则表达式3:匹配数字3;
-注：“整个返回数据”、“提取部分”均为提取范围"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【按需填写字段】
-格式
-1、当匹配规则不等于为空/不为空：
-（1）断言名称1:断言对象:断言表达式1:匹配规则:预期值1;
-（2）断言名称2:断言对象:断言表达式2:匹配规则:预期值2;
-2、当匹配规则等于为空/不为空：
-（1）断言名称1:断言对象:断言表达式1:匹配规则;
-（2）断言名称2:断言对象:断言表达式2:匹配规则;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>【按需填写字段】
-[请求体类型]非none时必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张三丰</t>
+  </si>
+  <si>
+    <t>json</t>
   </si>
 </sst>
 </file>
@@ -380,7 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,60 +439,63 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -838,140 +814,151 @@
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.6328125" defaultRowHeight="50" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:14" s="12" customFormat="1" ht="50" customHeight="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:14" s="11" customFormat="1" ht="50" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="9" t="s">
+      <c r="J1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="A2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>18</v>
+      <c r="E2" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="50" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="A3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>22</v>
+      <c r="J3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3" xr:uid="{E0DA7F06-B5F1-6449-B622-6BDC9BA0924A}">
+      <formula1>"json,xml,raw,form-data,x-www-form-urlencoded,none"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{6DB95AB1-BFDD-A64B-BAAD-473811CCAD4C}">
+      <formula1>"HTTP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{EE9ECA91-DE64-3F43-A3DD-9DAAF335204A}">
+      <formula1>"POST,GET,PUT,DELETE"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -981,26 +968,26 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
   <cols>
-    <col min="1" max="2" width="22.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="56.90625" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="10.6328125" style="3"/>
+    <col min="1" max="2" width="22.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="56.90625" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="10.6328125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="169" customHeight="1">
-      <c r="A1" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="15"/>
+      <c r="A1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1011,7 +998,7 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1022,28 +1009,28 @@
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="150">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="375">
-      <c r="A6" s="17"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>19</v>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/output/template/接口模板-HTTP.xlsx
+++ b/output/template/接口模板-HTTP.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/ForkRunner/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3CCE90-5642-0544-BD5A-7F1F61067D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4135D37E-FB27-4148-A630-152526029D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42340" yWindow="1640" windowWidth="36400" windowHeight="24260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HTTP模板" sheetId="6" r:id="rId1"/>
-    <sheet name="帮助" sheetId="2" r:id="rId2"/>
+    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HTTP模板!$A$1:$N$3</definedName>
@@ -476,6 +476,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -490,12 +496,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -859,46 +859,46 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -927,7 +927,7 @@
       <c r="H3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="13" t="s">
         <v>44</v>
       </c>
       <c r="J3" s="10" t="s">
@@ -947,15 +947,16 @@
       </c>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3" xr:uid="{E0DA7F06-B5F1-6449-B622-6BDC9BA0924A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{E0DA7F06-B5F1-6449-B622-6BDC9BA0924A}">
       <formula1>"json,xml,raw,form-data,x-www-form-urlencoded,none"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{6DB95AB1-BFDD-A64B-BAAD-473811CCAD4C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{6DB95AB1-BFDD-A64B-BAAD-473811CCAD4C}">
       <formula1>"HTTP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3" xr:uid="{EE9ECA91-DE64-3F43-A3DD-9DAAF335204A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{EE9ECA91-DE64-3F43-A3DD-9DAAF335204A}">
       <formula1>"POST,GET,PUT,DELETE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -974,11 +975,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="169" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
@@ -1014,7 +1015,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="150">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1025,7 +1026,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="375">
-      <c r="A6" s="16"/>
+      <c r="A6" s="18"/>
       <c r="B6" s="1" t="s">
         <v>17</v>
       </c>

--- a/output/template/接口模板-HTTP.xlsx
+++ b/output/template/接口模板-HTTP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/ForkRunner/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4135D37E-FB27-4148-A630-152526029D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFB4F8E-5FF0-C848-821C-36AE34E8D34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42340" yWindow="1640" windowWidth="36400" windowHeight="24260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,6 +38,9 @@
     <t>配置名称</t>
   </si>
   <si>
+    <t>请求体类型</t>
+  </si>
+  <si>
     <t>请求体</t>
   </si>
   <si>
@@ -142,9 +145,6 @@
   </si>
   <si>
     <t>协议类型</t>
-  </si>
-  <si>
-    <t>请求体类型</t>
   </si>
   <si>
     <t>【必输字段】
@@ -275,13 +275,14 @@
   </si>
   <si>
     <t>json</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="18"/>
       <color theme="1"/>
@@ -296,39 +297,26 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="仿宋"/>
-      <family val="3"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="仿宋"/>
-      <family val="3"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="MicrosoftYaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="MicrosoftYaHei"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -443,58 +431,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -812,151 +800,153 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63297404-CE5A-B446-8B7E-49D783A6BFDD}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="25.6328125" defaultRowHeight="50" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.6328125" defaultRowHeight="50" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="20.6328125" style="7"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="11" customFormat="1" ht="50" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:14" s="5" customFormat="1" ht="50" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="L1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="M1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="50" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="8" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
-  <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{E0DA7F06-B5F1-6449-B622-6BDC9BA0924A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{434C26E0-64F6-E544-A920-7E919BE114DE}">
       <formula1>"json,xml,raw,form-data,x-www-form-urlencoded,none"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{6DB95AB1-BFDD-A64B-BAAD-473811CCAD4C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{D4AD0D02-39FD-6C45-839C-22260A98FAF8}">
       <formula1>"HTTP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{EE9ECA91-DE64-3F43-A3DD-9DAAF335204A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{E5B2E656-BEAD-6848-B8BD-901452E2EA44}">
       <formula1>"POST,GET,PUT,DELETE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -967,71 +957,71 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="22.6328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="56.90625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="10.6328125" style="2"/>
+    <col min="1" max="2" width="20.6328125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="40.6328125" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="10.6328125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="169" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="12" t="s">
         <v>11</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="204" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="13" t="s">
         <v>13</v>
       </c>
+      <c r="B3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" ht="325">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    <row r="4" spans="1:3" ht="247">
+      <c r="A4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="114">
+      <c r="A5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="285">
+      <c r="A6" s="18"/>
+      <c r="B6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="150">
-      <c r="A5" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="375">
-      <c r="A6" s="18"/>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
